--- a/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.06%2375</t>
+          <t>+1.47%2410</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2375</v>
+        <v>2410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.60%588,000</t>
+          <t>13.69%588,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.60%</t>
+          <t>13.69%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.29%344</t>
+          <t>-1.31%339.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>344</v>
+        <v>339.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.97%1,448,000</t>
+          <t>4.88%1,448,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.97%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.29%246</t>
+          <t>+2.24%251.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>246</v>
+        <v>251.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.11%1,737,000</t>
+          <t>4.19%1,737,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.11%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.49%102</t>
+          <t>+0.49%102.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>102</v>
+        <v>102.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,12 +753,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.37%136.5</t>
+          <t>0%136.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.78%6325</t>
+          <t>-1.11%6255</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>6325</v>
+        <v>6255</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.33%53,000</t>
+          <t>3.29%53,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7750新代科技</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.19%2460</t>
+          <t>-3.66%5395</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2460</v>
+        <v>5395</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.67%108,000</t>
+          <t>2.69%49,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>108000</v>
+        <v>49000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2345智邦科技</t>
+          <t>7750新代科技</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.94%2105</t>
+          <t>-9.96%2215</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-9.96%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2105</v>
+        <v>2215</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.59%124,000</t>
+          <t>2.61%108,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>124000</v>
+        <v>108000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3105穩懋半導體</t>
+          <t>2345智邦科技</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+4.26%379</t>
+          <t>-3.33%2035</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+4.26%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>379</v>
+        <v>2035</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.35%656,000</t>
+          <t>2.56%124,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>656000</v>
+        <v>124000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>1504東元電機</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.63%5515</t>
+          <t>-1.37%72.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>-1.37%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5515</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.24%41,000</t>
+          <t>2.49%3,473,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>41000</v>
+        <v>3473000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>3105穩懋半導體</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.63%1555</t>
+          <t>-1.58%373</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>-1.58%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1555</v>
+        <v>373</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.23%148,000</t>
+          <t>2.44%656,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>148000</v>
+        <v>656000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+3.73%2780</t>
+          <t>+5.04%2920</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+3.73%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2780</v>
+        <v>2920</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.19%83,000</t>
+          <t>2.26%83,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-3.55%2985</t>
+          <t>-1.93%1525</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.55%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2985</v>
+        <v>1525</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.07%68,000</t>
+          <t>2.26%148,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.26%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>68000</v>
+        <v>148000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1%50.5</t>
+          <t>-0.4%50.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.06%4,181,000</t>
+          <t>2.07%4,181,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:24</t>
+          <t>2026-08-21 14:42:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1504東元電機</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+1.81%73.1</t>
+          <t>-4.02%2865</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.81%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>73.09999999999999</v>
+        <v>2865</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.02%2,856,000</t>
+          <t>1.99%68,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>2856000</v>
+        <v>68000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.16%6455</t>
+          <t>-0.77%6405</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6455</v>
+        <v>6405</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.97%31,000</t>
+          <t>1.96%31,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.96%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.34%590</t>
+          <t>-0.51%587</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.77%3700</t>
+          <t>+2.43%3790</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3700</v>
+        <v>3790</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.89%50,000</t>
+          <t>1.81%50,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.88%1140</t>
+          <t>-4.82%1085</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-4.82%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1140</v>
+        <v>1085</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.78%160,000</t>
+          <t>1.79%160,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,25 +1663,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>2610中華航空</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.56%5600</t>
+          <t>+2%20.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>+2%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5600</v>
+        <v>20.4</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.72%32,000</t>
+          <t>1.72%8,783,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1690,11 +1690,11 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>32000</v>
+        <v>8783000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2610中華航空</t>
+          <t>6147頎邦科技</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.5%20</t>
+          <t>-4.28%156.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-4.28%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20</v>
+        <v>156.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.72%8,783,000</t>
+          <t>1.63%1,019,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>8783000</v>
+        <v>1019000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6147頎邦科技</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+1.24%163.5</t>
+          <t>+0.24%206</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+1.24%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>163.5</v>
+        <v>206</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.62%1,019,000</t>
+          <t>1.59%788,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1019000</v>
+        <v>788000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>2059川湖科技</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.99%205.5</t>
+          <t>-3.88%13385</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>205.5</v>
+        <v>13385</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.56%788,000</t>
+          <t>1.50%11,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>788000</v>
+        <v>11000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2059川湖科技</t>
+          <t>6446藥華醫藥</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.21%13925</t>
+          <t>+1.82%1400</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+1.82%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13925</v>
+        <v>1400</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.53%11,000</t>
+          <t>1.46%108,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>11000</v>
+        <v>108000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>2308台達電子工業</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.07%1265</t>
+          <t>+0.29%1750</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.07%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1265</v>
+        <v>1750</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.49%116,000</t>
+          <t>1.40%82,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>116000</v>
+        <v>82000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6446藥華醫藥</t>
+          <t>2383台光電子材料</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.79%1375</t>
+          <t>-5.1%5680</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.79%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1375</v>
+        <v>5680</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.49%108,000</t>
+          <t>1.35%23,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>108000</v>
+        <v>23000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2308台達電子工業</t>
+          <t>1216統一企業</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.13%1745</t>
+          <t>-0.9%77.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1745</v>
+        <v>77.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.42%82,000</t>
+          <t>1.27%1,657,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>82000</v>
+        <v>1657000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2383台光電子材料</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.79%5985</t>
+          <t>-3.96%1090</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5985</v>
+        <v>1090</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.33%23,000</t>
+          <t>1.26%113,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>23000</v>
+        <v>113000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1216統一企業</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.9%78.2</t>
+          <t>-5.85%965</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.9%</t>
+          <t>-5.85%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>78.2</v>
+        <v>965</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.26%1,657,000</t>
+          <t>0.98%98,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1657000</v>
+        <v>98000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:25</t>
+          <t>2026-08-21 14:42:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>+2.13%528</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1135</v>
+        <v>528</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.26%113,000</t>
+          <t>0.98%193,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>113000</v>
+        <v>193000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-3.03%673</t>
+          <t>-3.57%649</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-3.57%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>673</v>
+        <v>649</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.00%146,000</t>
+          <t>0.96%146,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.44%1025</t>
+          <t>-5.53%1195</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.44%</t>
+          <t>-5.53%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1025</v>
+        <v>1195</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.00%98,000</t>
+          <t>0.69%56,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.69%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>98000</v>
+        <v>56000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+7.48%517</t>
+          <t>+1.72%5610</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+7.48%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>517</v>
+        <v>5610</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.91%193,000</t>
+          <t>0.65%12,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>193000</v>
+        <v>12000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.27%1195</t>
+          <t>-5.02%1135</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1195</v>
+        <v>1135</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2327國巨</t>
+          <t>4958臻鼎科技控股</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.43%562</t>
+          <t>-4.75%441</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>562</v>
+        <v>441</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.50%89,000</t>
+          <t>0.50%110,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>89000</v>
+        <v>110000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4958臻鼎科技控股</t>
+          <t>2327國巨</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.31%463</t>
+          <t>-1.42%554</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>463</v>
+        <v>554</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.49%110,000</t>
+          <t>0.49%89,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>110000</v>
+        <v>89000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+5.06%176.5</t>
+          <t>+2.55%181</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+5.06%</t>
+          <t>+2.55%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>176.5</v>
+        <v>181</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.40%243,000</t>
+          <t>0.42%243,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.42%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.53%1995</t>
+          <t>+4.01%2075</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+4.01%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1995</v>
+        <v>2075</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.49%2320</t>
+          <t>-0.43%2310</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.49%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2320</v>
+        <v>2310</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.28%12,000</t>
+          <t>0.27%12,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2891中國信託金融控股</t>
+          <t>2049上銀科技</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-2.31%63.4</t>
+          <t>-4.77%349</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-4.77%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>63.4</v>
+        <v>349</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.20%306,000</t>
+          <t>0.20%55,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>306000</v>
+        <v>55000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.05%57.7</t>
+          <t>-0.17%57.6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2049上銀科技</t>
+          <t>3665貿聯控股（BizLink Holding In</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-0.14%366.5</t>
+          <t>+1.11%2275</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>366.5</v>
+        <v>2275</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.20%55,000</t>
+          <t>0.20%9,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>55000</v>
+        <v>9000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%115.5</t>
+          <t>+0.87%116.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.39%128</t>
+          <t>+4.69%134</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.39%</t>
+          <t>+4.69%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:26</t>
+          <t>2026-08-21 14:42:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3665貿聯控股（BizLink Holding In</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+2.27%2250</t>
+          <t>+2.52%65</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+2.52%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2250</v>
+        <v>65</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.19%9,000</t>
+          <t>0.19%306,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9000</v>
+        <v>306000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:27</t>
+          <t>2026-08-21 14:42:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-2.21%2210</t>
+          <t>-2.49%2155</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2210</v>
+        <v>2155</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.18%8,000</t>
+          <t>0.17%8,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:27</t>
+          <t>2026-08-21 14:42:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.61%246.5</t>
+          <t>-0.41%245.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>246.5</v>
+        <v>245.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:27</t>
+          <t>2026-08-21 14:42:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.94%2140</t>
+          <t>-1.87%2100</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2140</v>
+        <v>2100</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:27</t>
+          <t>2026-08-21 14:42:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.02%993</t>
+          <t>-5.24%941</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-5.24%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>993</v>
+        <v>941</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:27</t>
+          <t>2026-08-21 14:42:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+0.24%851</t>
+          <t>-4.7%811</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>851</v>
+        <v>811</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:39</t>
+          <t>2026-08-21 14:51:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:40</t>
+          <t>2026-08-21 14:51:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:42</t>
+          <t>2026-08-21 14:51:43</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:43</t>
+          <t>2026-08-21 14:51:44</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:43</t>
+          <t>2026-08-21 14:51:44</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:43</t>
+          <t>2026-08-21 14:51:44</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:43</t>
+          <t>2026-08-21 14:51:44</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:43</t>
+          <t>2026-08-21 14:51:44</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:40</t>
+          <t>2026-08-21 14:55:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:41</t>
+          <t>2026-08-21 14:55:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:43</t>
+          <t>2026-08-21 14:55:06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:44</t>
+          <t>2026-08-21 14:55:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:44</t>
+          <t>2026-08-21 14:55:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:44</t>
+          <t>2026-08-21 14:55:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:44</t>
+          <t>2026-08-21 14:55:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:51:44</t>
+          <t>2026-08-21 14:55:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:03</t>
+          <t>2026-08-21 16:07:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:04</t>
+          <t>2026-08-21 16:07:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:06</t>
+          <t>2026-08-21 16:07:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:07</t>
+          <t>2026-08-21 16:07:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:07</t>
+          <t>2026-08-21 16:07:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:07</t>
+          <t>2026-08-21 16:07:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:07</t>
+          <t>2026-08-21 16:07:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:55:07</t>
+          <t>2026-08-21 16:07:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:37</t>
+          <t>2026-08-21 17:28:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:38</t>
+          <t>2026-08-21 17:28:20</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:39</t>
+          <t>2026-08-21 17:28:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:41</t>
+          <t>2026-08-21 17:28:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:41</t>
+          <t>2026-08-21 17:28:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:41</t>
+          <t>2026-08-21 17:28:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:41</t>
+          <t>2026-08-21 17:28:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:41</t>
+          <t>2026-08-21 17:28:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:19</t>
+          <t>2026-08-21 20:06:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:20</t>
+          <t>2026-08-21 20:06:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:21</t>
+          <t>2026-08-21 20:06:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:23</t>
+          <t>2026-08-21 20:06:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:23</t>
+          <t>2026-08-21 20:06:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:23</t>
+          <t>2026-08-21 20:06:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:23</t>
+          <t>2026-08-21 20:06:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:23</t>
+          <t>2026-08-21 20:06:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
